--- a/request_forms/003_material_request_form--request_forms.xlsx
+++ b/request_forms/003_material_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_0,_'name':_'paint'}</t>
+          <t>paint</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 0, 'name': 'Paint'}</t>
+          <t>Paint</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'tools'}</t>
+          <t>tools</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Tools'}</t>
+          <t>Tools</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'supplies'}</t>
+          <t>supplies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Supplies'}</t>
+          <t>Supplies</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_0,_'name':_'new_construction'}</t>
+          <t>new_construction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 0, 'name': 'New Construction'}</t>
+          <t>New Construction</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'renovation'}</t>
+          <t>renovation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Renovation'}</t>
+          <t>Renovation</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'repairs'}</t>
+          <t>repairs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Repairs'}</t>
+          <t>Repairs</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_0,_'name':_'builders'}</t>
+          <t>builders</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 0, 'name': 'Builders'}</t>
+          <t>Builders</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'architects'}</t>
+          <t>architects</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Architects'}</t>
+          <t>Architects</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'development_directors'}</t>
+          <t>development_directors</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Development Directors'}</t>
+          <t>Development Directors</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'property_managers'}</t>
+          <t>property_managers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Property Managers'}</t>
+          <t>Property Managers</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_0,_'name':_'paint'}</t>
+          <t>paint</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 0, 'name': 'Paint'}</t>
+          <t>Paint</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'tools'}</t>
+          <t>tools</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Tools'}</t>
+          <t>Tools</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'supplies'}</t>
+          <t>supplies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Supplies'}</t>
+          <t>Supplies</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_0,_'name':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 0, 'name': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_0,_'name':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 0, 'name': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
